--- a/data/tuning COM translasi roll kaki 1.xlsx
+++ b/data/tuning COM translasi roll kaki 1.xlsx
@@ -470,7 +470,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.117</v>
+        <v>0.164</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>128.028</v>
+        <v>127.662</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>-5.965</v>
       </c>
       <c r="G3" t="n">
-        <v>-37.387</v>
+        <v>-35.808</v>
       </c>
       <c r="H3" t="n">
-        <v>193.73</v>
+        <v>194.578</v>
       </c>
     </row>
     <row r="4">
@@ -522,7 +522,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>256.03</v>
+        <v>255.689</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -534,13 +534,13 @@
         <v>198.868</v>
       </c>
       <c r="F4" t="n">
-        <v>-8.76</v>
+        <v>-5.965</v>
       </c>
       <c r="G4" t="n">
-        <v>-20.153</v>
+        <v>-10.245</v>
       </c>
       <c r="H4" t="n">
-        <v>196.985</v>
+        <v>198.958</v>
       </c>
     </row>
     <row r="5">
@@ -548,7 +548,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>384.023</v>
+        <v>383.643</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -560,13 +560,13 @@
         <v>198.868</v>
       </c>
       <c r="F5" t="n">
-        <v>-8.769</v>
+        <v>-5.965</v>
       </c>
       <c r="G5" t="n">
-        <v>-7.343</v>
+        <v>5.83</v>
       </c>
       <c r="H5" t="n">
-        <v>199.009</v>
+        <v>200.316</v>
       </c>
     </row>
     <row r="6">
@@ -574,7 +574,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>512.0700000000001</v>
+        <v>511.828</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -589,10 +589,10 @@
         <v>-5.965</v>
       </c>
       <c r="G6" t="n">
-        <v>5.512</v>
+        <v>16.087</v>
       </c>
       <c r="H6" t="n">
-        <v>199.307</v>
+        <v>199.652</v>
       </c>
     </row>
     <row r="7">
@@ -600,7 +600,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>640.022</v>
+        <v>639.6319999999999</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -615,10 +615,10 @@
         <v>-5.965</v>
       </c>
       <c r="G7" t="n">
-        <v>15.681</v>
+        <v>25.755</v>
       </c>
       <c r="H7" t="n">
-        <v>198.625</v>
+        <v>199.086</v>
       </c>
     </row>
     <row r="8">
@@ -626,7 +626,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>768.004</v>
+        <v>767.622</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -638,13 +638,13 @@
         <v>198.868</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.965</v>
+        <v>-8.839</v>
       </c>
       <c r="G8" t="n">
-        <v>20.309</v>
+        <v>41.42</v>
       </c>
       <c r="H8" t="n">
-        <v>199.401</v>
+        <v>197.853</v>
       </c>
     </row>
     <row r="9">
@@ -652,7 +652,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>896.026</v>
+        <v>895.59</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -664,13 +664,13 @@
         <v>198.868</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.965</v>
+        <v>-8.829000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>31.782</v>
+        <v>45.015</v>
       </c>
       <c r="H9" t="n">
-        <v>199.467</v>
+        <v>196.034</v>
       </c>
     </row>
     <row r="10">
@@ -678,7 +678,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1024.024</v>
+        <v>1023.671</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -690,13 +690,13 @@
         <v>198.868</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.965</v>
+        <v>-8.831</v>
       </c>
       <c r="G10" t="n">
-        <v>34.895</v>
+        <v>35.372</v>
       </c>
       <c r="H10" t="n">
-        <v>198.626</v>
+        <v>197.951</v>
       </c>
     </row>
     <row r="11">
@@ -704,7 +704,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1151.984</v>
+        <v>1151.613</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -716,13 +716,13 @@
         <v>198.868</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.965</v>
+        <v>-8.834</v>
       </c>
       <c r="G11" t="n">
-        <v>35.479</v>
+        <v>19.859</v>
       </c>
       <c r="H11" t="n">
-        <v>197.866</v>
+        <v>200.171</v>
       </c>
     </row>
     <row r="12">
@@ -730,7 +730,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1279.956</v>
+        <v>1279.591</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -742,13 +742,13 @@
         <v>198.868</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.824</v>
+        <v>-8.832000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>33.836</v>
+        <v>8.311999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>198.284</v>
+        <v>200.974</v>
       </c>
     </row>
     <row r="13">
@@ -756,7 +756,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1407.952</v>
+        <v>1407.604</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -768,13 +768,13 @@
         <v>198.868</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.818</v>
+        <v>-8.834</v>
       </c>
       <c r="G13" t="n">
-        <v>31.58</v>
+        <v>5.079</v>
       </c>
       <c r="H13" t="n">
-        <v>198.154</v>
+        <v>201.259</v>
       </c>
     </row>
     <row r="14">
@@ -782,7 +782,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1535.956</v>
+        <v>1535.565</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -794,13 +794,13 @@
         <v>198.868</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.815</v>
+        <v>-8.836</v>
       </c>
       <c r="G14" t="n">
-        <v>20.365</v>
+        <v>7.775</v>
       </c>
       <c r="H14" t="n">
-        <v>199.541</v>
+        <v>201.321</v>
       </c>
     </row>
     <row r="15">
@@ -808,7 +808,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1663.98</v>
+        <v>1663.66</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -820,13 +820,13 @@
         <v>198.868</v>
       </c>
       <c r="F15" t="n">
-        <v>-8.811</v>
+        <v>-8.839</v>
       </c>
       <c r="G15" t="n">
-        <v>15.004</v>
+        <v>7.251</v>
       </c>
       <c r="H15" t="n">
-        <v>199.774</v>
+        <v>201.687</v>
       </c>
     </row>
     <row r="16">
@@ -834,7 +834,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1791.994</v>
+        <v>1791.555</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -846,13 +846,13 @@
         <v>198.868</v>
       </c>
       <c r="F16" t="n">
-        <v>-8.811</v>
+        <v>-11.715</v>
       </c>
       <c r="G16" t="n">
-        <v>9.119999999999999</v>
+        <v>12.889</v>
       </c>
       <c r="H16" t="n">
-        <v>200.195</v>
+        <v>201.381</v>
       </c>
     </row>
     <row r="17">
@@ -860,7 +860,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1920.023</v>
+        <v>1919.585</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -872,13 +872,13 @@
         <v>198.868</v>
       </c>
       <c r="F17" t="n">
-        <v>-8.811</v>
+        <v>-11.72</v>
       </c>
       <c r="G17" t="n">
-        <v>3.226</v>
+        <v>15.61</v>
       </c>
       <c r="H17" t="n">
-        <v>200.41</v>
+        <v>201.337</v>
       </c>
     </row>
     <row r="18">
@@ -886,7 +886,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2047.947</v>
+        <v>2047.522</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -898,13 +898,13 @@
         <v>198.868</v>
       </c>
       <c r="F18" t="n">
-        <v>-8.813000000000001</v>
+        <v>-11.72</v>
       </c>
       <c r="G18" t="n">
-        <v>0.001</v>
+        <v>15.61</v>
       </c>
       <c r="H18" t="n">
-        <v>200.603</v>
+        <v>201.337</v>
       </c>
     </row>
   </sheetData>

--- a/data/tuning COM translasi roll kaki 1.xlsx
+++ b/data/tuning COM translasi roll kaki 1.xlsx
@@ -470,25 +470,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.164</v>
+        <v>0.116</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>14.514</v>
+        <v>15.482</v>
       </c>
       <c r="E2" t="n">
-        <v>198.868</v>
+        <v>198.824</v>
       </c>
       <c r="F2" t="n">
-        <v>-7</v>
+        <v>-9.757</v>
       </c>
       <c r="G2" t="n">
-        <v>-35.518</v>
+        <v>-35.52</v>
       </c>
       <c r="H2" t="n">
-        <v>191.103</v>
+        <v>190.981</v>
       </c>
     </row>
     <row r="3">
@@ -496,25 +496,25 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>127.662</v>
+        <v>143.472</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>14.514</v>
+        <v>15.482</v>
       </c>
       <c r="E3" t="n">
-        <v>198.868</v>
+        <v>198.824</v>
       </c>
       <c r="F3" t="n">
-        <v>-5.965</v>
+        <v>-8.766</v>
       </c>
       <c r="G3" t="n">
-        <v>-35.808</v>
+        <v>-36.753</v>
       </c>
       <c r="H3" t="n">
-        <v>194.578</v>
+        <v>193.559</v>
       </c>
     </row>
     <row r="4">
@@ -522,25 +522,25 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>255.689</v>
+        <v>271.396</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>14.514</v>
+        <v>15.482</v>
       </c>
       <c r="E4" t="n">
-        <v>198.868</v>
+        <v>198.824</v>
       </c>
       <c r="F4" t="n">
-        <v>-5.965</v>
+        <v>-8.769</v>
       </c>
       <c r="G4" t="n">
-        <v>-10.245</v>
+        <v>-24.045</v>
       </c>
       <c r="H4" t="n">
-        <v>198.958</v>
+        <v>196.489</v>
       </c>
     </row>
     <row r="5">
@@ -548,25 +548,25 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>383.643</v>
+        <v>399.415</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>14.514</v>
+        <v>15.482</v>
       </c>
       <c r="E5" t="n">
-        <v>198.868</v>
+        <v>198.824</v>
       </c>
       <c r="F5" t="n">
-        <v>-5.965</v>
+        <v>-8.775</v>
       </c>
       <c r="G5" t="n">
-        <v>5.83</v>
+        <v>-13.961</v>
       </c>
       <c r="H5" t="n">
-        <v>200.316</v>
+        <v>198.348</v>
       </c>
     </row>
     <row r="6">
@@ -574,25 +574,25 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>511.828</v>
+        <v>527.449</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>14.514</v>
+        <v>15.482</v>
       </c>
       <c r="E6" t="n">
-        <v>198.868</v>
+        <v>198.824</v>
       </c>
       <c r="F6" t="n">
         <v>-5.965</v>
       </c>
       <c r="G6" t="n">
-        <v>16.087</v>
+        <v>-4.12</v>
       </c>
       <c r="H6" t="n">
-        <v>199.652</v>
+        <v>199.047</v>
       </c>
     </row>
     <row r="7">
@@ -600,25 +600,25 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>639.6319999999999</v>
+        <v>655.38</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>14.514</v>
+        <v>15.482</v>
       </c>
       <c r="E7" t="n">
-        <v>198.868</v>
+        <v>198.824</v>
       </c>
       <c r="F7" t="n">
         <v>-5.965</v>
       </c>
       <c r="G7" t="n">
-        <v>25.755</v>
+        <v>3.876</v>
       </c>
       <c r="H7" t="n">
-        <v>199.086</v>
+        <v>199.589</v>
       </c>
     </row>
     <row r="8">
@@ -626,25 +626,25 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>767.622</v>
+        <v>783.393</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>14.514</v>
+        <v>15.482</v>
       </c>
       <c r="E8" t="n">
-        <v>198.868</v>
+        <v>198.824</v>
       </c>
       <c r="F8" t="n">
-        <v>-8.839</v>
+        <v>-5.965</v>
       </c>
       <c r="G8" t="n">
-        <v>41.42</v>
+        <v>12.187</v>
       </c>
       <c r="H8" t="n">
-        <v>197.853</v>
+        <v>199.574</v>
       </c>
     </row>
     <row r="9">
@@ -652,25 +652,25 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>895.59</v>
+        <v>911.374</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>14.514</v>
+        <v>15.482</v>
       </c>
       <c r="E9" t="n">
-        <v>198.868</v>
+        <v>198.824</v>
       </c>
       <c r="F9" t="n">
-        <v>-8.829000000000001</v>
+        <v>-5.965</v>
       </c>
       <c r="G9" t="n">
-        <v>45.015</v>
+        <v>19.533</v>
       </c>
       <c r="H9" t="n">
-        <v>196.034</v>
+        <v>200.3</v>
       </c>
     </row>
     <row r="10">
@@ -678,25 +678,25 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1023.671</v>
+        <v>1039.414</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>14.514</v>
+        <v>15.482</v>
       </c>
       <c r="E10" t="n">
-        <v>198.868</v>
+        <v>198.824</v>
       </c>
       <c r="F10" t="n">
-        <v>-8.831</v>
+        <v>-5.965</v>
       </c>
       <c r="G10" t="n">
-        <v>35.372</v>
+        <v>26.098</v>
       </c>
       <c r="H10" t="n">
-        <v>197.951</v>
+        <v>200.224</v>
       </c>
     </row>
     <row r="11">
@@ -704,25 +704,25 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1151.613</v>
+        <v>1167.401</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>14.514</v>
+        <v>15.482</v>
       </c>
       <c r="E11" t="n">
-        <v>198.868</v>
+        <v>198.824</v>
       </c>
       <c r="F11" t="n">
-        <v>-8.834</v>
+        <v>-5.965</v>
       </c>
       <c r="G11" t="n">
-        <v>19.859</v>
+        <v>29.039</v>
       </c>
       <c r="H11" t="n">
-        <v>200.171</v>
+        <v>199.742</v>
       </c>
     </row>
     <row r="12">
@@ -730,25 +730,25 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1279.591</v>
+        <v>1295.357</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>14.514</v>
+        <v>15.482</v>
       </c>
       <c r="E12" t="n">
-        <v>198.868</v>
+        <v>198.824</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.832000000000001</v>
+        <v>-5.965</v>
       </c>
       <c r="G12" t="n">
-        <v>8.311999999999999</v>
+        <v>32.167</v>
       </c>
       <c r="H12" t="n">
-        <v>200.974</v>
+        <v>198.957</v>
       </c>
     </row>
     <row r="13">
@@ -756,25 +756,25 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1407.604</v>
+        <v>1423.377</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>14.514</v>
+        <v>15.482</v>
       </c>
       <c r="E13" t="n">
-        <v>198.868</v>
+        <v>198.824</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.834</v>
+        <v>-5.965</v>
       </c>
       <c r="G13" t="n">
-        <v>5.079</v>
+        <v>32.366</v>
       </c>
       <c r="H13" t="n">
-        <v>201.259</v>
+        <v>198.707</v>
       </c>
     </row>
     <row r="14">
@@ -782,25 +782,25 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1535.565</v>
+        <v>1551.426</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>14.514</v>
+        <v>15.482</v>
       </c>
       <c r="E14" t="n">
-        <v>198.868</v>
+        <v>198.824</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.836</v>
+        <v>-5.965</v>
       </c>
       <c r="G14" t="n">
-        <v>7.775</v>
+        <v>32.777</v>
       </c>
       <c r="H14" t="n">
-        <v>201.321</v>
+        <v>198.217</v>
       </c>
     </row>
     <row r="15">
@@ -808,25 +808,25 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1663.66</v>
+        <v>1679.376</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>14.514</v>
+        <v>15.482</v>
       </c>
       <c r="E15" t="n">
-        <v>198.868</v>
+        <v>198.824</v>
       </c>
       <c r="F15" t="n">
-        <v>-8.839</v>
+        <v>-5.965</v>
       </c>
       <c r="G15" t="n">
-        <v>7.251</v>
+        <v>30.078</v>
       </c>
       <c r="H15" t="n">
-        <v>201.687</v>
+        <v>198.529</v>
       </c>
     </row>
     <row r="16">
@@ -834,25 +834,25 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1791.555</v>
+        <v>1807.341</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>14.514</v>
+        <v>15.482</v>
       </c>
       <c r="E16" t="n">
-        <v>198.868</v>
+        <v>198.824</v>
       </c>
       <c r="F16" t="n">
-        <v>-11.715</v>
+        <v>-5.965</v>
       </c>
       <c r="G16" t="n">
-        <v>12.889</v>
+        <v>24.689</v>
       </c>
       <c r="H16" t="n">
-        <v>201.381</v>
+        <v>199.033</v>
       </c>
     </row>
     <row r="17">
@@ -860,25 +860,25 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1919.585</v>
+        <v>1935.336</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>14.514</v>
+        <v>15.482</v>
       </c>
       <c r="E17" t="n">
-        <v>198.868</v>
+        <v>198.824</v>
       </c>
       <c r="F17" t="n">
-        <v>-11.72</v>
+        <v>-5.965</v>
       </c>
       <c r="G17" t="n">
-        <v>15.61</v>
+        <v>25.784</v>
       </c>
       <c r="H17" t="n">
-        <v>201.337</v>
+        <v>199.252</v>
       </c>
     </row>
     <row r="18">
@@ -886,25 +886,25 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2047.522</v>
+        <v>2063.32</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14.514</v>
+        <v>15.482</v>
       </c>
       <c r="E18" t="n">
-        <v>198.868</v>
+        <v>198.824</v>
       </c>
       <c r="F18" t="n">
-        <v>-11.72</v>
+        <v>-8.816000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>15.61</v>
+        <v>20.118</v>
       </c>
       <c r="H18" t="n">
-        <v>201.337</v>
+        <v>199.744</v>
       </c>
     </row>
   </sheetData>
